--- a/tests/testdata/excel/日付.xlsx
+++ b/tests/testdata/excel/日付.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{200D3E5E-ECFA-40E5-8A55-F9CDF557D661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5537C3E0-96BB-44BD-9863-FB734AF30419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{5438F0CF-923C-4ACA-B044-506D63D56514}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{9858B819-3ED8-4736-8DD5-76F64C7ACA11}"/>
   </bookViews>
   <sheets>
     <sheet name="日付" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6D4461A-1363-4993-8EC4-5C26AD4E50F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45CBB16-984B-458E-BAF8-A22CBAA0B313}">
   <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
